--- a/resources/data-imports/Monsters/twisted-memories-monsters.xlsx
+++ b/resources/data-imports/Monsters/twisted-memories-monsters.xlsx
@@ -644,37 +644,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1006,7 +1006,7 @@
         <v>0.2546985</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>1000000000</v>
+        <v>25</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -1024,16 +1024,16 @@
         <v>2000000000</v>
       </c>
       <c r="AC2" s="1" t="n">
-        <v>0.4561317</v>
+        <v>0.001</v>
       </c>
       <c r="AD2" s="1" t="n">
-        <v>0.4561317</v>
+        <v>0.001</v>
       </c>
       <c r="AE2" s="1" t="n">
-        <v>0.4561317</v>
+        <v>0.001</v>
       </c>
       <c r="AF2" s="1" t="n">
-        <v>0.4561317</v>
+        <v>0.001</v>
       </c>
       <c r="AG2" s="1" t="n">
         <v>0.35455049</v>
@@ -1066,7 +1066,7 @@
         <v>0.10293</v>
       </c>
       <c r="AW2" s="1" t="n">
-        <v>0.35455049</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1128,7 +1128,7 @@
         <v>0.259485303609</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>1024378141</v>
+        <v>34</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1146,16 +1146,16 @@
         <v>2048756281</v>
       </c>
       <c r="AC3" s="1" t="n">
-        <v>0.4623469505442</v>
+        <v>0.001123</v>
       </c>
       <c r="AD3" s="1" t="n">
-        <v>0.4623469505442</v>
+        <v>0.001123</v>
       </c>
       <c r="AE3" s="1" t="n">
-        <v>0.4623469505442</v>
+        <v>0.001123</v>
       </c>
       <c r="AF3" s="1" t="n">
-        <v>0.4623469505442</v>
+        <v>0.001123</v>
       </c>
       <c r="AG3" s="1" t="n">
         <v>0.359160142740686</v>
@@ -1188,7 +1188,7 @@
         <v>0.105945849</v>
       </c>
       <c r="AW3" s="1" t="n">
-        <v>0.359160142740686</v>
+        <v>0.001123</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1250,7 +1250,7 @@
         <v>0.264362070405028</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>1049350575</v>
+        <v>47</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1268,16 +1268,16 @@
         <v>2098701149</v>
       </c>
       <c r="AC4" s="1" t="n">
-        <v>0.468646890092315</v>
+        <v>0.001262</v>
       </c>
       <c r="AD4" s="1" t="n">
-        <v>0.468646890092315</v>
+        <v>0.001262</v>
       </c>
       <c r="AE4" s="1" t="n">
-        <v>0.468646890092315</v>
+        <v>0.001262</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>0.468646890092315</v>
+        <v>0.001262</v>
       </c>
       <c r="AG4" s="1" t="n">
         <v>0.363829727420515</v>
@@ -1310,7 +1310,7 @@
         <v>0.1090500623757</v>
       </c>
       <c r="AW4" s="1" t="n">
-        <v>0.363829727420515</v>
+        <v>0.001262</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1372,7 +1372,7 @@
         <v>0.26933049115622</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>1074931790</v>
+        <v>65</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1390,16 +1390,16 @@
         <v>2149863580</v>
       </c>
       <c r="AC5" s="1" t="n">
-        <v>0.475032672616713</v>
+        <v>0.001417</v>
       </c>
       <c r="AD5" s="1" t="n">
-        <v>0.475032672616713</v>
+        <v>0.001417</v>
       </c>
       <c r="AE5" s="1" t="n">
-        <v>0.475032672616713</v>
+        <v>0.001417</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0.475032672616713</v>
+        <v>0.001417</v>
       </c>
       <c r="AG5" s="1" t="n">
         <v>0.3685600232386</v>
@@ -1432,7 +1432,7 @@
         <v>0.112245229203308</v>
       </c>
       <c r="AW5" s="1" t="n">
-        <v>0.3685600232386</v>
+        <v>0.001417</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1494,7 +1494,7 @@
         <v>0.27439228840701</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>1101136628</v>
+        <v>89</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>2202273255</v>
       </c>
       <c r="AC6" s="1" t="n">
-        <v>0.481505467813788</v>
+        <v>0.001592</v>
       </c>
       <c r="AD6" s="1" t="n">
-        <v>0.481505467813788</v>
+        <v>0.001592</v>
       </c>
       <c r="AE6" s="1" t="n">
-        <v>0.481505467813788</v>
+        <v>0.001592</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0.481505467813788</v>
+        <v>0.001592</v>
       </c>
       <c r="AG6" s="1" t="n">
         <v>0.373351819524734</v>
@@ -1554,7 +1554,7 @@
         <v>0.115534014418965</v>
       </c>
       <c r="AW6" s="1" t="n">
-        <v>0.373351819524734</v>
+        <v>0.001592</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1616,7 +1616,7 @@
         <v>0.279549217075331</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>1127980291</v>
+        <v>122</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1634,16 +1634,16 @@
         <v>2255960581</v>
       </c>
       <c r="AC7" s="1" t="n">
-        <v>0.488066461318219</v>
+        <v>0.001789</v>
       </c>
       <c r="AD7" s="1" t="n">
-        <v>0.488066461318219</v>
+        <v>0.001789</v>
       </c>
       <c r="AE7" s="1" t="n">
-        <v>0.488066461318219</v>
+        <v>0.001789</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0.488066461318219</v>
+        <v>0.001789</v>
       </c>
       <c r="AG7" s="1" t="n">
         <v>0.378205915871103</v>
@@ -1676,7 +1676,7 @@
         <v>0.118919161041441</v>
       </c>
       <c r="AW7" s="1" t="n">
-        <v>0.378205915871103</v>
+        <v>0.001789</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1744,7 +1744,7 @@
         <v>0.284803065061045</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>1155478353</v>
+        <v>168</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>0</v>
@@ -1762,16 +1762,16 @@
         <v>2310956705</v>
       </c>
       <c r="AC8" s="1" t="n">
-        <v>0.494716854920141</v>
+        <v>0.002009</v>
       </c>
       <c r="AD8" s="1" t="n">
-        <v>0.494716854920141</v>
+        <v>0.002009</v>
       </c>
       <c r="AE8" s="1" t="n">
-        <v>0.494716854920141</v>
+        <v>0.002009</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.494716854920141</v>
+        <v>0.002009</v>
       </c>
       <c r="AG8" s="1" t="n">
         <v>0.38312312226571</v>
@@ -1804,7 +1804,7 @@
         <v>0.122403492459955</v>
       </c>
       <c r="AW8" s="1" t="n">
-        <v>0.38312312226571</v>
+        <v>0.002009</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1872,7 +1872,7 @@
         <v>0.290155653865802</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>1183646766</v>
+        <v>231</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -1890,16 +1890,16 @@
         <v>2367293531</v>
       </c>
       <c r="AC9" s="1" t="n">
-        <v>0.501457866785283</v>
+        <v>0.002257</v>
       </c>
       <c r="AD9" s="1" t="n">
-        <v>0.501457866785283</v>
+        <v>0.002257</v>
       </c>
       <c r="AE9" s="1" t="n">
-        <v>0.501457866785283</v>
+        <v>0.002257</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.501457866785283</v>
+        <v>0.002257</v>
       </c>
       <c r="AG9" s="1" t="n">
         <v>0.388104259227535</v>
@@ -1938,7 +1938,7 @@
         <v>0.125989914789032</v>
       </c>
       <c r="AW9" s="1" t="n">
-        <v>0.388104259227535</v>
+        <v>0.002257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2000,7 +2000,7 @@
         <v>0.295608839224556</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>1212501873</v>
+        <v>317</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
@@ -2018,16 +2018,16 @@
         <v>2425003745</v>
       </c>
       <c r="AC10" s="1" t="n">
-        <v>0.508290731678099</v>
+        <v>0.002535</v>
       </c>
       <c r="AD10" s="1" t="n">
-        <v>0.508290731678099</v>
+        <v>0.002535</v>
       </c>
       <c r="AE10" s="1" t="n">
-        <v>0.508290731678099</v>
+        <v>0.002535</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0.508290731678099</v>
+        <v>0.002535</v>
       </c>
       <c r="AG10" s="1" t="n">
         <v>0.393150157943456</v>
@@ -2060,7 +2060,7 @@
         <v>0.12968141929235</v>
       </c>
       <c r="AW10" s="1" t="n">
-        <v>0.393150157943456</v>
+        <v>0.002535</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2122,7 +2122,7 @@
         <v>0.301164511748942</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>1242060413</v>
+        <v>436</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>2484120826</v>
       </c>
       <c r="AC11" s="1" t="n">
-        <v>0.515216701187945</v>
+        <v>0.002848</v>
       </c>
       <c r="AD11" s="1" t="n">
-        <v>0.515216701187945</v>
+        <v>0.002848</v>
       </c>
       <c r="AE11" s="1" t="n">
-        <v>0.515216701187945</v>
+        <v>0.002848</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0.515216701187945</v>
+        <v>0.002848</v>
       </c>
       <c r="AG11" s="1" t="n">
         <v>0.398261660406942</v>
@@ -2182,7 +2182,7 @@
         <v>0.133481084877616</v>
       </c>
       <c r="AW11" s="1" t="n">
-        <v>0.398261660406942</v>
+        <v>0.002848</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2244,7 +2244,7 @@
         <v>0.306824597582752</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1272339536</v>
+        <v>599</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>0</v>
@@ -2262,16 +2262,16 @@
         <v>2544679072</v>
       </c>
       <c r="AC12" s="1" t="n">
-        <v>0.522237043958332</v>
+        <v>0.003199</v>
       </c>
       <c r="AD12" s="1" t="n">
-        <v>0.522237043958332</v>
+        <v>0.003199</v>
       </c>
       <c r="AE12" s="1" t="n">
-        <v>0.522237043958332</v>
+        <v>0.003199</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0.522237043958332</v>
+        <v>0.003199</v>
       </c>
       <c r="AG12" s="1" t="n">
         <v>0.403439619558557</v>
@@ -2304,7 +2304,7 @@
         <v>0.13739208066453</v>
       </c>
       <c r="AW12" s="1" t="n">
-        <v>0.403439619558557</v>
+        <v>0.003199</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2366,7 +2366,7 @@
         <v>0.312591059069722</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>1303356808</v>
+        <v>823</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>0</v>
@@ -2384,16 +2384,16 @@
         <v>2606713615</v>
       </c>
       <c r="AC13" s="1" t="n">
-        <v>0.529353045919308</v>
+        <v>0.003594</v>
       </c>
       <c r="AD13" s="1" t="n">
-        <v>0.529353045919308</v>
+        <v>0.003594</v>
       </c>
       <c r="AE13" s="1" t="n">
-        <v>0.529353045919308</v>
+        <v>0.003594</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0.529353045919308</v>
+        <v>0.003594</v>
       </c>
       <c r="AG13" s="1" t="n">
         <v>0.408684899428286</v>
@@ -2426,7 +2426,7 @@
         <v>0.141417668628001</v>
       </c>
       <c r="AW13" s="1" t="n">
-        <v>0.408684899428286</v>
+        <v>0.003594</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2488,7 +2488,7 @@
         <v>0.318465895433878</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1335130223</v>
+        <v>1130</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>0</v>
@@ -2506,16 +2506,16 @@
         <v>2670260445</v>
       </c>
       <c r="AC14" s="1" t="n">
-        <v>0.536566010523004</v>
+        <v>0.004037</v>
       </c>
       <c r="AD14" s="1" t="n">
-        <v>0.536566010523004</v>
+        <v>0.004037</v>
       </c>
       <c r="AE14" s="1" t="n">
-        <v>0.536566010523004</v>
+        <v>0.004037</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>0.536566010523004</v>
+        <v>0.004037</v>
       </c>
       <c r="AG14" s="1" t="n">
         <v>0.413998375279713</v>
@@ -2548,7 +2548,7 @@
         <v>0.145561206318801</v>
       </c>
       <c r="AW14" s="1" t="n">
-        <v>0.413998375279713</v>
+        <v>0.004037</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2610,7 +2610,7 @@
         <v>0.324451143472663</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>1367678215</v>
+        <v>1553</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>0</v>
@@ -2628,16 +2628,16 @@
         <v>2735356429</v>
       </c>
       <c r="AC15" s="1" t="n">
-        <v>0.543877258982391</v>
+        <v>0.004535</v>
       </c>
       <c r="AD15" s="1" t="n">
-        <v>0.543877258982391</v>
+        <v>0.004535</v>
       </c>
       <c r="AE15" s="1" t="n">
-        <v>0.543877258982391</v>
+        <v>0.004535</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>0.543877258982391</v>
+        <v>0.004535</v>
       </c>
       <c r="AG15" s="1" t="n">
         <v>0.419380933756074</v>
@@ -2670,7 +2670,7 @@
         <v>0.149826149663942</v>
       </c>
       <c r="AW15" s="1" t="n">
-        <v>0.419380933756074</v>
+        <v>0.004535</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2732,7 +2732,7 @@
         <v>0.330548878263088</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>1401019666</v>
+        <v>2133</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>0</v>
@@ -2750,16 +2750,16 @@
         <v>2802039331</v>
       </c>
       <c r="AC16" s="1" t="n">
-        <v>0.551288130513285</v>
+        <v>0.005094</v>
       </c>
       <c r="AD16" s="1" t="n">
-        <v>0.551288130513285</v>
+        <v>0.005094</v>
       </c>
       <c r="AE16" s="1" t="n">
-        <v>0.551288130513285</v>
+        <v>0.005094</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0.551288130513285</v>
+        <v>0.005094</v>
       </c>
       <c r="AG16" s="1" t="n">
         <v>0.42483347302821</v>
@@ -2792,7 +2792,7 @@
         <v>0.154216055849096</v>
       </c>
       <c r="AW16" s="1" t="n">
-        <v>0.42483347302821</v>
+        <v>0.005094</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2854,7 +2854,7 @@
         <v>0.336761213881164</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>1435173920</v>
+        <v>2930</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>0</v>
@@ -2872,16 +2872,16 @@
         <v>2870347839</v>
       </c>
       <c r="AC17" s="1" t="n">
-        <v>0.558799982579659</v>
+        <v>0.005723</v>
       </c>
       <c r="AD17" s="1" t="n">
-        <v>0.558799982579659</v>
+        <v>0.005723</v>
       </c>
       <c r="AE17" s="1" t="n">
-        <v>0.558799982579659</v>
+        <v>0.005723</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.558799982579659</v>
+        <v>0.005723</v>
       </c>
       <c r="AG17" s="1" t="n">
         <v>0.430356902944439</v>
@@ -2914,7 +2914,7 @@
         <v>0.158734586285474</v>
       </c>
       <c r="AW17" s="1" t="n">
-        <v>0.430356902944439</v>
+        <v>0.005723</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2976,7 +2976,7 @@
         <v>0.343090304134847</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>1470160791</v>
+        <v>4026</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>0</v>
@@ -2994,16 +2994,16 @@
         <v>2940321581</v>
       </c>
       <c r="AC18" s="1" t="n">
-        <v>0.566414191142289</v>
+        <v>0.006429</v>
       </c>
       <c r="AD18" s="1" t="n">
-        <v>0.566414191142289</v>
+        <v>0.006429</v>
       </c>
       <c r="AE18" s="1" t="n">
-        <v>0.566414191142289</v>
+        <v>0.006429</v>
       </c>
       <c r="AF18" s="1" t="n">
-        <v>0.566414191142289</v>
+        <v>0.006429</v>
       </c>
       <c r="AG18" s="1" t="n">
         <v>0.435952145182381</v>
@@ -3036,7 +3036,7 @@
         <v>0.163385509663639</v>
       </c>
       <c r="AW18" s="1" t="n">
-        <v>0.435952145182381</v>
+        <v>0.006429</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3098,7 +3098,7 @@
         <v>0.349538343310757</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>1506000577</v>
+        <v>5531</v>
       </c>
       <c r="X19" s="1" t="n">
         <v>0</v>
@@ -3116,16 +3116,16 @@
         <v>3012001153</v>
       </c>
       <c r="AC19" s="1" t="n">
-        <v>0.574132150910794</v>
+        <v>0.007221</v>
       </c>
       <c r="AD19" s="1" t="n">
-        <v>0.574132150910794</v>
+        <v>0.007221</v>
       </c>
       <c r="AE19" s="1" t="n">
-        <v>0.574132150910794</v>
+        <v>0.007221</v>
       </c>
       <c r="AF19" s="1" t="n">
-        <v>0.574132150910794</v>
+        <v>0.007221</v>
       </c>
       <c r="AG19" s="1" t="n">
         <v>0.441620133402755</v>
@@ -3158,7 +3158,7 @@
         <v>0.168172705096784</v>
       </c>
       <c r="AW19" s="1" t="n">
-        <v>0.441620133402755</v>
+        <v>0.007221</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3226,7 +3226,7 @@
         <v>0.35610756693494</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>1542714070</v>
+        <v>7598</v>
       </c>
       <c r="X20" s="1" t="n">
         <v>0</v>
@@ -3244,16 +3244,16 @@
         <v>3085428139</v>
       </c>
       <c r="AC20" s="1" t="n">
-        <v>0.581955275599104</v>
+        <v>0.008112</v>
       </c>
       <c r="AD20" s="1" t="n">
-        <v>0.581955275599104</v>
+        <v>0.008112</v>
       </c>
       <c r="AE20" s="1" t="n">
-        <v>0.581955275599104</v>
+        <v>0.008112</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0.581955275599104</v>
+        <v>0.008112</v>
       </c>
       <c r="AG20" s="1" t="n">
         <v>0.447361813405178</v>
@@ -3286,7 +3286,7 @@
         <v>0.173100165356119</v>
       </c>
       <c r="AW20" s="1" t="n">
-        <v>0.447361813405178</v>
+        <v>0.008112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3348,7 +3348,7 @@
         <v>0.362800252547915</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>1580322570</v>
+        <v>10438</v>
       </c>
       <c r="X21" s="1" t="n">
         <v>0</v>
@@ -3366,16 +3366,16 @@
         <v>3160645139</v>
       </c>
       <c r="AC21" s="1" t="n">
-        <v>0.589884998184418</v>
+        <v>0.009112</v>
       </c>
       <c r="AD21" s="1" t="n">
-        <v>0.589884998184418</v>
+        <v>0.009112</v>
       </c>
       <c r="AE21" s="1" t="n">
-        <v>0.589884998184418</v>
+        <v>0.009112</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0.589884998184418</v>
+        <v>0.009112</v>
       </c>
       <c r="AG21" s="1" t="n">
         <v>0.453178143285984</v>
@@ -3408,7 +3408,7 @@
         <v>0.178172000201054</v>
       </c>
       <c r="AW21" s="1" t="n">
-        <v>0.453178143285984</v>
+        <v>0.009112</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3470,7 +3470,7 @@
         <v>0.3696187204943</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>1618847895</v>
+        <v>14340</v>
       </c>
       <c r="X22" s="1" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>3237695789</v>
       </c>
       <c r="AC22" s="1" t="n">
-        <v>0.597922771169678</v>
+        <v>0.010236</v>
       </c>
       <c r="AD22" s="1" t="n">
-        <v>0.597922771169678</v>
+        <v>0.010236</v>
       </c>
       <c r="AE22" s="1" t="n">
-        <v>0.597922771169678</v>
+        <v>0.010236</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>0.597922771169678</v>
+        <v>0.010236</v>
       </c>
       <c r="AG22" s="1" t="n">
         <v>0.459070093598103</v>
@@ -3530,7 +3530,7 @@
         <v>0.183392439806944</v>
       </c>
       <c r="AW22" s="1" t="n">
-        <v>0.459070093598103</v>
+        <v>0.010236</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3592,7 +3592,7 @@
         <v>0.37656533472727</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>1658312396</v>
+        <v>19701</v>
       </c>
       <c r="X23" s="1" t="n">
         <v>0</v>
@@ -3610,16 +3610,16 @@
         <v>3316624791</v>
       </c>
       <c r="AC23" s="1" t="n">
-        <v>0.606070066849636</v>
+        <v>0.011499</v>
       </c>
       <c r="AD23" s="1" t="n">
-        <v>0.606070066849636</v>
+        <v>0.011499</v>
       </c>
       <c r="AE23" s="1" t="n">
-        <v>0.606070066849636</v>
+        <v>0.011499</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>0.606070066849636</v>
+        <v>0.011499</v>
       </c>
       <c r="AG23" s="1" t="n">
         <v>0.465038647513009</v>
@@ -3652,7 +3652,7 @@
         <v>0.188765838293288</v>
       </c>
       <c r="AW23" s="1" t="n">
-        <v>0.465038647513009</v>
+        <v>0.011499</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3714,7 +3714,7 @@
         <v>0.383642503628135</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>2123677966</v>
+        <v>27066</v>
       </c>
       <c r="X24" s="1" t="n">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         <v>4247355932</v>
       </c>
       <c r="AC24" s="1" t="n">
-        <v>0.61432837758053</v>
+        <v>0.012917</v>
       </c>
       <c r="AD24" s="1" t="n">
-        <v>0.61432837758053</v>
+        <v>0.012917</v>
       </c>
       <c r="AE24" s="1" t="n">
-        <v>0.61432837758053</v>
+        <v>0.012917</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0.61432837758053</v>
+        <v>0.012917</v>
       </c>
       <c r="AG24" s="1" t="n">
         <v>0.471084800984785</v>
@@ -3774,7 +3774,7 @@
         <v>0.194296677355281</v>
       </c>
       <c r="AW24" s="1" t="n">
-        <v>0.471084800984785</v>
+        <v>0.012917</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3836,7 +3836,7 @@
         <v>0.390852680841322</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>2197638868</v>
+        <v>37184</v>
       </c>
       <c r="X25" s="1" t="n">
         <v>0</v>
@@ -3854,16 +3854,16 @@
         <v>4395277736</v>
       </c>
       <c r="AC25" s="1" t="n">
-        <v>0.622699216053442</v>
+        <v>0.01451</v>
       </c>
       <c r="AD25" s="1" t="n">
-        <v>0.622699216053442</v>
+        <v>0.01451</v>
       </c>
       <c r="AE25" s="1" t="n">
-        <v>0.622699216053442</v>
+        <v>0.01451</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>0.622699216053442</v>
+        <v>0.01451</v>
       </c>
       <c r="AG25" s="1" t="n">
         <v>0.477209562916308</v>
@@ -3896,7 +3896,7 @@
         <v>0.199989570001791</v>
       </c>
       <c r="AW25" s="1" t="n">
-        <v>0.477209562916308</v>
+        <v>0.01451</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3958,7 +3958,7 @@
         <v>0.398198366125053</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>2274175591</v>
+        <v>51084</v>
       </c>
       <c r="X26" s="1" t="n">
         <v>0</v>
@@ -3976,16 +3976,16 @@
         <v>4548351182</v>
       </c>
       <c r="AC26" s="1" t="n">
-        <v>0.631184115571386</v>
+        <v>0.016299</v>
       </c>
       <c r="AD26" s="1" t="n">
-        <v>0.631184115571386</v>
+        <v>0.016299</v>
       </c>
       <c r="AE26" s="1" t="n">
-        <v>0.631184115571386</v>
+        <v>0.016299</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>0.631184115571386</v>
+        <v>0.016299</v>
       </c>
       <c r="AG26" s="1" t="n">
         <v>0.483413955327608</v>
@@ -4018,7 +4018,7 @@
         <v>0.205849264402844</v>
       </c>
       <c r="AW26" s="1" t="n">
-        <v>0.483413955327608</v>
+        <v>0.016299</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4086,7 +4086,7 @@
         <v>0.405682106218008</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>2353377843</v>
+        <v>70180</v>
       </c>
       <c r="X27" s="1" t="n">
         <v>0</v>
@@ -4104,16 +4104,16 @@
         <v>4706755686</v>
       </c>
       <c r="AC27" s="1" t="n">
-        <v>0.639784630330162</v>
+        <v>0.01831</v>
       </c>
       <c r="AD27" s="1" t="n">
-        <v>0.639784630330162</v>
+        <v>0.01831</v>
       </c>
       <c r="AE27" s="1" t="n">
-        <v>0.639784630330162</v>
+        <v>0.01831</v>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>0.639784630330162</v>
+        <v>0.01831</v>
       </c>
       <c r="AG27" s="1" t="n">
         <v>0.489699013526405</v>
@@ -4152,7 +4152,7 @@
         <v>0.211880647849847</v>
       </c>
       <c r="AW27" s="1" t="n">
-        <v>0.489699013526405</v>
+        <v>0.01831</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4214,7 +4214,7 @@
         <v>0.413306495722269</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>2435338456</v>
+        <v>96416</v>
       </c>
       <c r="X28" s="1" t="n">
         <v>0</v>
@@ -4232,16 +4232,16 @@
         <v>4870676912</v>
       </c>
       <c r="AC28" s="1" t="n">
-        <v>0.64850233570304</v>
+        <v>0.020568</v>
       </c>
       <c r="AD28" s="1" t="n">
-        <v>0.64850233570304</v>
+        <v>0.020568</v>
       </c>
       <c r="AE28" s="1" t="n">
-        <v>0.64850233570304</v>
+        <v>0.020568</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0.64850233570304</v>
+        <v>0.020568</v>
       </c>
       <c r="AG28" s="1" t="n">
         <v>0.496065786280867</v>
@@ -4274,7 +4274,7 @@
         <v>0.218088750831847</v>
       </c>
       <c r="AW28" s="1" t="n">
-        <v>0.496065786280867</v>
+        <v>0.020568</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4336,7 +4336,7 @@
         <v>0.421074178002873</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>2520153495</v>
+        <v>132458</v>
       </c>
       <c r="X29" s="1" t="n">
         <v>0</v>
@@ -4354,16 +4354,16 @@
         <v>5040306990</v>
       </c>
       <c r="AC29" s="1" t="n">
-        <v>0.65733882852933</v>
+        <v>0.023104</v>
       </c>
       <c r="AD29" s="1" t="n">
-        <v>0.65733882852933</v>
+        <v>0.023104</v>
       </c>
       <c r="AE29" s="1" t="n">
-        <v>0.65733882852933</v>
+        <v>0.023104</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>0.65733882852933</v>
+        <v>0.023104</v>
       </c>
       <c r="AG29" s="1" t="n">
         <v>0.502515335994619</v>
@@ -4396,7 +4396,7 @@
         <v>0.224478751231221</v>
       </c>
       <c r="AW29" s="1" t="n">
-        <v>0.502515335994619</v>
+        <v>0.023104</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4458,7 +4458,7 @@
         <v>0.428987846104259</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>2607922370</v>
+        <v>181974</v>
       </c>
       <c r="X30" s="1" t="n">
         <v>0</v>
@@ -4476,16 +4476,16 @@
         <v>5215844739</v>
       </c>
       <c r="AC30" s="1" t="n">
-        <v>0.66629572740687</v>
+        <v>0.025954</v>
       </c>
       <c r="AD30" s="1" t="n">
-        <v>0.66629572740687</v>
+        <v>0.025954</v>
       </c>
       <c r="AE30" s="1" t="n">
-        <v>0.66629572740687</v>
+        <v>0.025954</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>0.66629572740687</v>
+        <v>0.025954</v>
       </c>
       <c r="AG30" s="1" t="n">
         <v>0.50904873888402</v>
@@ -4518,7 +4518,7 @@
         <v>0.231055978642295</v>
       </c>
       <c r="AW30" s="1" t="n">
-        <v>0.50904873888402</v>
+        <v>0.025954</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4580,7 +4580,7 @@
         <v>0.437050243683943</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>2698747953</v>
+        <v>250000</v>
       </c>
       <c r="X31" s="1" t="n">
         <v>0</v>
@@ -4598,16 +4598,16 @@
         <v>5397495906</v>
       </c>
       <c r="AC31" s="1" t="n">
-        <v>0.675374672988516</v>
+        <v>0.029155</v>
       </c>
       <c r="AD31" s="1" t="n">
-        <v>0.675374672988516</v>
+        <v>0.029155</v>
       </c>
       <c r="AE31" s="1" t="n">
-        <v>0.675374672988516</v>
+        <v>0.029155</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>0.675374672988516</v>
+        <v>0.029155</v>
       </c>
       <c r="AG31" s="1" t="n">
         <v>0.515667085157746</v>
@@ -4640,7 +4640,7 @@
         <v>0.237825918816515</v>
       </c>
       <c r="AW31" s="1" t="n">
-        <v>0.515667085157746</v>
+        <v>0.029155</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4702,7 +4702,7 @@
         <v>0.445264165963739</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>2750000000</v>
+        <v>343456</v>
       </c>
       <c r="X32" s="1" t="n">
         <v>0</v>
@@ -4720,16 +4720,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC32" s="1" t="n">
-        <v>0.684577328282658</v>
+        <v>0.03275</v>
       </c>
       <c r="AD32" s="1" t="n">
-        <v>0.684577328282658</v>
+        <v>0.03275</v>
       </c>
       <c r="AE32" s="1" t="n">
-        <v>0.684577328282658</v>
+        <v>0.03275</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>0.684577328282658</v>
+        <v>0.03275</v>
       </c>
       <c r="AG32" s="1" t="n">
         <v>0.522371479198716</v>
@@ -4762,7 +4762,7 @@
         <v>0.244794218237839</v>
       </c>
       <c r="AW32" s="1" t="n">
-        <v>0.522371479198716</v>
+        <v>0.03275</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4824,7 +4824,7 @@
         <v>0.453632460698861</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>2750000000</v>
+        <v>471848</v>
       </c>
       <c r="X33" s="1" t="n">
         <v>0</v>
@@ -4842,16 +4842,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC33" s="1" t="n">
-        <v>0.693905378957837</v>
+        <v>0.03679</v>
       </c>
       <c r="AD33" s="1" t="n">
-        <v>0.693905378957837</v>
+        <v>0.03679</v>
       </c>
       <c r="AE33" s="1" t="n">
-        <v>0.693905378957837</v>
+        <v>0.03679</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0.693905378957837</v>
+        <v>0.03679</v>
       </c>
       <c r="AG33" s="1" t="n">
         <v>0.529163039748371</v>
@@ -4884,7 +4884,7 @@
         <v>0.251966688832207</v>
       </c>
       <c r="AW33" s="1" t="n">
-        <v>0.529163039748371</v>
+        <v>0.03679</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4946,7 +4946,7 @@
         <v>0.462158029165236</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>2750000000</v>
+        <v>648236</v>
       </c>
       <c r="X34" s="1" t="n">
         <v>0</v>
@@ -4964,16 +4964,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC34" s="1" t="n">
-        <v>0.703360533651517</v>
+        <v>0.041327</v>
       </c>
       <c r="AD34" s="1" t="n">
-        <v>0.703360533651517</v>
+        <v>0.041327</v>
       </c>
       <c r="AE34" s="1" t="n">
-        <v>0.703360533651517</v>
+        <v>0.041327</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.703360533651517</v>
+        <v>0.041327</v>
       </c>
       <c r="AG34" s="1" t="n">
         <v>0.536042900093355</v>
@@ -5006,7 +5006,7 @@
         <v>0.259349312814991</v>
       </c>
       <c r="AW34" s="1" t="n">
-        <v>0.536042900093355</v>
+        <v>0.041327</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5068,7 +5068,7 @@
         <v>0.470843827165367</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>2750000000</v>
+        <v>890562</v>
       </c>
       <c r="X35" s="1" t="n">
         <v>0</v>
@@ -5086,16 +5086,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC35" s="1" t="n">
-        <v>0.712944524283052</v>
+        <v>0.046424</v>
       </c>
       <c r="AD35" s="1" t="n">
-        <v>0.712944524283052</v>
+        <v>0.046424</v>
       </c>
       <c r="AE35" s="1" t="n">
-        <v>0.712944524283052</v>
+        <v>0.046424</v>
       </c>
       <c r="AF35" s="1" t="n">
-        <v>0.712944524283052</v>
+        <v>0.046424</v>
       </c>
       <c r="AG35" s="1" t="n">
         <v>0.543012208254629</v>
@@ -5128,7 +5128,7 @@
         <v>0.26694824768047</v>
       </c>
       <c r="AW35" s="1" t="n">
-        <v>0.543012208254629</v>
+        <v>0.046424</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5190,7 +5190,7 @@
         <v>0.479692866053113</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>2750000000</v>
+        <v>1223475</v>
       </c>
       <c r="X36" s="1" t="n">
         <v>0</v>
@@ -5208,16 +5208,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC36" s="1" t="n">
-        <v>0.722659106370933</v>
+        <v>0.052149</v>
       </c>
       <c r="AD36" s="1" t="n">
-        <v>0.722659106370933</v>
+        <v>0.052149</v>
       </c>
       <c r="AE36" s="1" t="n">
-        <v>0.722659106370933</v>
+        <v>0.052149</v>
       </c>
       <c r="AF36" s="1" t="n">
-        <v>0.722659106370933</v>
+        <v>0.052149</v>
       </c>
       <c r="AG36" s="1" t="n">
         <v>0.550072127179031</v>
@@ -5250,7 +5250,7 @@
         <v>0.274769831337508</v>
       </c>
       <c r="AW36" s="1" t="n">
-        <v>0.550072127179031</v>
+        <v>0.052149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5318,7 +5318,7 @@
         <v>0.488708213777715</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>2750000000</v>
+        <v>1680839</v>
       </c>
       <c r="X37" s="1" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC37" s="1" t="n">
-        <v>0.732506059354343</v>
+        <v>0.05858</v>
       </c>
       <c r="AD37" s="1" t="n">
-        <v>0.732506059354343</v>
+        <v>0.05858</v>
       </c>
       <c r="AE37" s="1" t="n">
-        <v>0.732506059354343</v>
+        <v>0.05858</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.732506059354343</v>
+        <v>0.05858</v>
       </c>
       <c r="AG37" s="1" t="n">
         <v>0.557223834933336</v>
@@ -5378,7 +5378,7 @@
         <v>0.282820587395697</v>
       </c>
       <c r="AW37" s="1" t="n">
-        <v>0.557223834933336</v>
+        <v>0.05858</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5440,7 +5440,7 @@
         <v>0.497892995947453</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>2750000000</v>
+        <v>2309177</v>
       </c>
       <c r="X38" s="1" t="n">
         <v>0</v>
@@ -5458,16 +5458,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC38" s="1" t="n">
-        <v>0.742487186919106</v>
+        <v>0.065805</v>
       </c>
       <c r="AD38" s="1" t="n">
-        <v>0.742487186919106</v>
+        <v>0.065805</v>
       </c>
       <c r="AE38" s="1" t="n">
-        <v>0.742487186919106</v>
+        <v>0.065805</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.742487186919106</v>
+        <v>0.065805</v>
       </c>
       <c r="AG38" s="1" t="n">
         <v>0.564468524900838</v>
@@ -5500,7 +5500,7 @@
         <v>0.291107230606391</v>
       </c>
       <c r="AW38" s="1" t="n">
-        <v>0.564468524900838</v>
+        <v>0.065805</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5562,7 +5562,7 @@
         <v>0.50725039691329</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>2750000000</v>
+        <v>3172402</v>
       </c>
       <c r="X39" s="1" t="n">
         <v>0</v>
@@ -5580,16 +5580,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC39" s="1" t="n">
-        <v>0.752604317328065</v>
+        <v>0.073921</v>
       </c>
       <c r="AD39" s="1" t="n">
-        <v>0.752604317328065</v>
+        <v>0.073921</v>
       </c>
       <c r="AE39" s="1" t="n">
-        <v>0.752604317328065</v>
+        <v>0.073921</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.752604317328065</v>
+        <v>0.073921</v>
       </c>
       <c r="AG39" s="1" t="n">
         <v>0.571807405980484</v>
@@ -5622,7 +5622,7 @@
         <v>0.299636672463158</v>
       </c>
       <c r="AW39" s="1" t="n">
-        <v>0.571807405980484</v>
+        <v>0.073921</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5684,7 +5684,7 @@
         <v>0.516783660872878</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>2750000000</v>
+        <v>4358322</v>
       </c>
       <c r="X40" s="1" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC40" s="1" t="n">
-        <v>0.762859303755977</v>
+        <v>0.083038</v>
       </c>
       <c r="AD40" s="1" t="n">
-        <v>0.762859303755977</v>
+        <v>0.083038</v>
       </c>
       <c r="AE40" s="1" t="n">
-        <v>0.762859303755977</v>
+        <v>0.083038</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>0.762859303755977</v>
+        <v>0.083038</v>
       </c>
       <c r="AG40" s="1" t="n">
         <v>0.579241702788599</v>
@@ -5744,7 +5744,7 @@
         <v>0.308416026966329</v>
       </c>
       <c r="AW40" s="1" t="n">
-        <v>0.579241702788599</v>
+        <v>0.083038</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5806,7 +5806,7 @@
         <v>0.526496092995323</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>2750000000</v>
+        <v>5987566</v>
       </c>
       <c r="X41" s="1" t="n">
         <v>0</v>
@@ -5824,16 +5824,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC41" s="1" t="n">
-        <v>0.773254024628956</v>
+        <v>0.093279</v>
       </c>
       <c r="AD41" s="1" t="n">
-        <v>0.773254024628956</v>
+        <v>0.093279</v>
       </c>
       <c r="AE41" s="1" t="n">
-        <v>0.773254024628956</v>
+        <v>0.093279</v>
       </c>
       <c r="AF41" s="1" t="n">
-        <v>0.773254024628956</v>
+        <v>0.093279</v>
       </c>
       <c r="AG41" s="1" t="n">
         <v>0.586772655863235</v>
@@ -5866,7 +5866,7 @@
         <v>0.317452616556442</v>
       </c>
       <c r="AW41" s="1" t="n">
-        <v>0.586772655863235</v>
+        <v>0.093279</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5928,7 +5928,7 @@
         <v>0.536391060567077</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>2750000000</v>
+        <v>8225861</v>
       </c>
       <c r="X42" s="1" t="n">
         <v>0</v>
@@ -5946,16 +5946,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC42" s="1" t="n">
-        <v>0.78379038396855</v>
+        <v>0.104783</v>
       </c>
       <c r="AD42" s="1" t="n">
-        <v>0.78379038396855</v>
+        <v>0.104783</v>
       </c>
       <c r="AE42" s="1" t="n">
-        <v>0.78379038396855</v>
+        <v>0.104783</v>
       </c>
       <c r="AF42" s="1" t="n">
-        <v>0.78379038396855</v>
+        <v>0.104783</v>
       </c>
       <c r="AG42" s="1" t="n">
         <v>0.594401521871175</v>
@@ -5988,7 +5988,7 @@
         <v>0.326753978221546</v>
       </c>
       <c r="AW42" s="1" t="n">
-        <v>0.594401521871175</v>
+        <v>0.104783</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6050,7 +6050,7 @@
         <v>0.546471994159375</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>2750000000</v>
+        <v>11300884</v>
       </c>
       <c r="X43" s="1" t="n">
         <v>0</v>
@@ -6068,16 +6068,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC43" s="1" t="n">
-        <v>0.794470311740506</v>
+        <v>0.117705</v>
       </c>
       <c r="AD43" s="1" t="n">
-        <v>0.794470311740506</v>
+        <v>0.117705</v>
       </c>
       <c r="AE43" s="1" t="n">
-        <v>0.794470311740506</v>
+        <v>0.117705</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.794470311740506</v>
+        <v>0.117705</v>
       </c>
       <c r="AG43" s="1" t="n">
         <v>0.602129573817631</v>
@@ -6110,7 +6110,7 @@
         <v>0.336327869783437</v>
       </c>
       <c r="AW43" s="1" t="n">
-        <v>0.602129573817631</v>
+        <v>0.117705</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6178,7 +6178,7 @@
         <v>0.556742388817606</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>2750000000</v>
+        <v>15525423</v>
       </c>
       <c r="X44" s="1" t="n">
         <v>0</v>
@@ -6196,16 +6196,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC44" s="1" t="n">
-        <v>0.805295764208282</v>
+        <v>0.132222</v>
       </c>
       <c r="AD44" s="1" t="n">
-        <v>0.805295764208282</v>
+        <v>0.132222</v>
       </c>
       <c r="AE44" s="1" t="n">
-        <v>0.805295764208282</v>
+        <v>0.132222</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.805295764208282</v>
+        <v>0.132222</v>
       </c>
       <c r="AG44" s="1" t="n">
         <v>0.609958101258663</v>
@@ -6238,7 +6238,7 @@
         <v>0.346182276368092</v>
       </c>
       <c r="AW44" s="1" t="n">
-        <v>0.609958101258663</v>
+        <v>0.132222</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6306,7 +6306,7 @@
         <v>0.567205805273044</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>2750000000</v>
+        <v>21329196</v>
       </c>
       <c r="X45" s="1" t="n">
         <v>0</v>
@@ -6324,16 +6324,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC45" s="1" t="n">
-        <v>0.816268724291384</v>
+        <v>0.148529</v>
       </c>
       <c r="AD45" s="1" t="n">
-        <v>0.816268724291384</v>
+        <v>0.148529</v>
       </c>
       <c r="AE45" s="1" t="n">
-        <v>0.816268724291384</v>
+        <v>0.148529</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.816268724291384</v>
+        <v>0.148529</v>
       </c>
       <c r="AG45" s="1" t="n">
         <v>0.617888410516368</v>
@@ -6366,7 +6366,7 @@
         <v>0.356325417065677</v>
       </c>
       <c r="AW45" s="1" t="n">
-        <v>0.617888410516368</v>
+        <v>0.148529</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6434,7 +6434,7 @@
         <v>0.577865871177346</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>2750000000</v>
+        <v>29302557</v>
       </c>
       <c r="X46" s="1" t="n">
         <v>0</v>
@@ -6452,16 +6452,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC46" s="1" t="n">
-        <v>0.827391201928578</v>
+        <v>0.166847</v>
       </c>
       <c r="AD46" s="1" t="n">
-        <v>0.827391201928578</v>
+        <v>0.166847</v>
       </c>
       <c r="AE46" s="1" t="n">
-        <v>0.827391201928578</v>
+        <v>0.166847</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>0.827391201928578</v>
+        <v>0.166847</v>
       </c>
       <c r="AG46" s="1" t="n">
         <v>0.625921824896855</v>
@@ -6494,7 +6494,7 @@
         <v>0.366765751785702</v>
       </c>
       <c r="AW46" s="1" t="n">
-        <v>0.625921824896855</v>
+        <v>0.166847</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6562,7 +6562,7 @@
         <v>0.588726282360253</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>2750000000</v>
+        <v>40256550</v>
       </c>
       <c r="X47" s="1" t="n">
         <v>0</v>
@@ -6580,16 +6580,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC47" s="1" t="n">
-        <v>0.838665234446057</v>
+        <v>0.187424</v>
       </c>
       <c r="AD47" s="1" t="n">
-        <v>0.838665234446057</v>
+        <v>0.187424</v>
       </c>
       <c r="AE47" s="1" t="n">
-        <v>0.838665234446057</v>
+        <v>0.187424</v>
       </c>
       <c r="AF47" s="1" t="n">
-        <v>0.838665234446057</v>
+        <v>0.187424</v>
       </c>
       <c r="AG47" s="1" t="n">
         <v>0.634059684911069</v>
@@ -6622,7 +6622,7 @@
         <v>0.377511988313023</v>
       </c>
       <c r="AW47" s="1" t="n">
-        <v>0.634059684911069</v>
+        <v>0.187424</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6690,7 +6690,7 @@
         <v>0.599790804110931</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>2750000000</v>
+        <v>55305406</v>
       </c>
       <c r="X48" s="1" t="n">
         <v>0</v>
@@ -6708,16 +6708,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC48" s="1" t="n">
-        <v>0.850092886930619</v>
+        <v>0.210539</v>
       </c>
       <c r="AD48" s="1" t="n">
-        <v>0.850092886930619</v>
+        <v>0.210539</v>
       </c>
       <c r="AE48" s="1" t="n">
-        <v>0.850092886930619</v>
+        <v>0.210539</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.850092886930619</v>
+        <v>0.210539</v>
       </c>
       <c r="AG48" s="1" t="n">
         <v>0.642303348498472</v>
@@ -6750,7 +6750,7 @@
         <v>0.388573089570594</v>
       </c>
       <c r="AW48" s="1" t="n">
-        <v>0.642303348498472</v>
+        <v>0.210539</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6818,7 +6818,7 @@
         <v>0.611063272483392</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>2750000000</v>
+        <v>75979882</v>
       </c>
       <c r="X49" s="1" t="n">
         <v>0</v>
@@ -6836,16 +6836,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC49" s="1" t="n">
-        <v>0.861676252607935</v>
+        <v>0.236505</v>
       </c>
       <c r="AD49" s="1" t="n">
-        <v>0.861676252607935</v>
+        <v>0.236505</v>
       </c>
       <c r="AE49" s="1" t="n">
-        <v>0.861676252607935</v>
+        <v>0.236505</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>0.861676252607935</v>
+        <v>0.236505</v>
       </c>
       <c r="AG49" s="1" t="n">
         <v>0.65065419125364</v>
@@ -6878,7 +6878,7 @@
         <v>0.399958281095013</v>
       </c>
       <c r="AW49" s="1" t="n">
-        <v>0.65065419125364</v>
+        <v>0.236505</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6946,7 +6946,7 @@
         <v>0.622547595626445</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>2750000000</v>
+        <v>104382970</v>
       </c>
       <c r="X50" s="1" t="n">
         <v>0</v>
@@ -6964,16 +6964,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC50" s="1" t="n">
-        <v>0.873417453225971</v>
+        <v>0.265673</v>
       </c>
       <c r="AD50" s="1" t="n">
-        <v>0.873417453225971</v>
+        <v>0.265673</v>
       </c>
       <c r="AE50" s="1" t="n">
-        <v>0.873417453225971</v>
+        <v>0.265673</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>0.873417453225971</v>
+        <v>0.265673</v>
       </c>
       <c r="AG50" s="1" t="n">
         <v>0.659113606655805</v>
@@ -7006,7 +7006,7 @@
         <v>0.411677058731097</v>
       </c>
       <c r="AW50" s="1" t="n">
-        <v>0.659113606655805</v>
+        <v>0.265673</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7074,7 +7074,7 @@
         <v>0.634247755138648</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>2750000000</v>
+        <v>143403808</v>
       </c>
       <c r="X51" s="1" t="n">
         <v>0</v>
@@ -7092,16 +7092,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC51" s="1" t="n">
-        <v>0.885318639443628</v>
+        <v>0.298438</v>
       </c>
       <c r="AD51" s="1" t="n">
-        <v>0.885318639443628</v>
+        <v>0.298438</v>
       </c>
       <c r="AE51" s="1" t="n">
-        <v>0.885318639443628</v>
+        <v>0.298438</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0.885318639443628</v>
+        <v>0.298438</v>
       </c>
       <c r="AG51" s="1" t="n">
         <v>0.66768300630138</v>
@@ -7134,7 +7134,7 @@
         <v>0.423739196551918</v>
       </c>
       <c r="AW51" s="1" t="n">
-        <v>0.66768300630138</v>
+        <v>0.298438</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7202,7 +7202,7 @@
         <v>0.646167807448724</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>2750000000</v>
+        <v>197011564</v>
       </c>
       <c r="X52" s="1" t="n">
         <v>0</v>
@@ -7220,16 +7220,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC52" s="1" t="n">
-        <v>0.897381991224687</v>
+        <v>0.335244</v>
       </c>
       <c r="AD52" s="1" t="n">
-        <v>0.897381991224687</v>
+        <v>0.335244</v>
       </c>
       <c r="AE52" s="1" t="n">
-        <v>0.897381991224687</v>
+        <v>0.335244</v>
       </c>
       <c r="AF52" s="1" t="n">
-        <v>0.897381991224687</v>
+        <v>0.335244</v>
       </c>
       <c r="AG52" s="1" t="n">
         <v>0.676363820139507</v>
@@ -7262,7 +7262,7 @@
         <v>0.436154755010889</v>
       </c>
       <c r="AW52" s="1" t="n">
-        <v>0.676363820139507</v>
+        <v>0.335244</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7330,7 +7330,7 @@
         <v>0.658311885221915</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>2750000000</v>
+        <v>270659175</v>
       </c>
       <c r="X53" s="1" t="n">
         <v>0</v>
@@ -7348,16 +7348,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC53" s="1" t="n">
-        <v>0.909609718237114</v>
+        <v>0.37659</v>
       </c>
       <c r="AD53" s="1" t="n">
-        <v>0.909609718237114</v>
+        <v>0.37659</v>
       </c>
       <c r="AE53" s="1" t="n">
-        <v>0.909609718237114</v>
+        <v>0.37659</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>0.909609718237114</v>
+        <v>0.37659</v>
       </c>
       <c r="AG53" s="1" t="n">
         <v>0.685157496710669</v>
@@ -7390,7 +7390,7 @@
         <v>0.448934089332708</v>
       </c>
       <c r="AW53" s="1" t="n">
-        <v>0.685157496710669</v>
+        <v>0.37659</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7458,7 +7458,7 @@
         <v>0.670684198792776</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>2750000000</v>
+        <v>371838014</v>
       </c>
       <c r="X54" s="1" t="n">
         <v>0</v>
@@ -7476,16 +7476,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC54" s="1" t="n">
-        <v>0.922004060257813</v>
+        <v>0.423034</v>
       </c>
       <c r="AD54" s="1" t="n">
-        <v>0.922004060257813</v>
+        <v>0.423034</v>
       </c>
       <c r="AE54" s="1" t="n">
-        <v>0.922004060257813</v>
+        <v>0.423034</v>
       </c>
       <c r="AF54" s="1" t="n">
-        <v>0.922004060257813</v>
+        <v>0.423034</v>
       </c>
       <c r="AG54" s="1" t="n">
         <v>0.694065503388403</v>
@@ -7518,7 +7518,7 @@
         <v>0.462087858150157</v>
       </c>
       <c r="AW54" s="1" t="n">
-        <v>0.694065503388403</v>
+        <v>0.423034</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7586,7 +7586,7 @@
         <v>0.683289037624888</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>2750000000</v>
+        <v>510839912</v>
       </c>
       <c r="X55" s="1" t="n">
         <v>0</v>
@@ -7604,16 +7604,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC55" s="1" t="n">
-        <v>0.934567287582886</v>
+        <v>0.475207</v>
       </c>
       <c r="AD55" s="1" t="n">
-        <v>0.934567287582886</v>
+        <v>0.475207</v>
       </c>
       <c r="AE55" s="1" t="n">
-        <v>0.934567287582886</v>
+        <v>0.475207</v>
       </c>
       <c r="AF55" s="1" t="n">
-        <v>0.934567287582886</v>
+        <v>0.475207</v>
       </c>
       <c r="AG55" s="1" t="n">
         <v>0.703089326624157</v>
@@ -7646,7 +7646,7 @@
         <v>0.475627032393956</v>
       </c>
       <c r="AW55" s="1" t="n">
-        <v>0.703089326624157</v>
+        <v>0.475207</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7714,7 +7714,7 @@
         <v>0.69613077179801</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>2750000000</v>
+        <v>701804027</v>
       </c>
       <c r="X56" s="1" t="n">
         <v>0</v>
@@ -7732,16 +7732,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC56" s="1" t="n">
-        <v>0.94730170144349</v>
+        <v>0.533814</v>
       </c>
       <c r="AD56" s="1" t="n">
-        <v>0.94730170144349</v>
+        <v>0.533814</v>
       </c>
       <c r="AE56" s="1" t="n">
-        <v>0.94730170144349</v>
+        <v>0.533814</v>
       </c>
       <c r="AF56" s="1" t="n">
-        <v>0.94730170144349</v>
+        <v>0.533814</v>
       </c>
       <c r="AG56" s="1" t="n">
         <v>0.712230472195328</v>
@@ -7774,7 +7774,7 @@
         <v>0.489562904443099</v>
       </c>
       <c r="AW56" s="1" t="n">
-        <v>0.712230472195328</v>
+        <v>0.533814</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7842,7 +7842,7 @@
         <v>0.709213853523181</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>2750000000</v>
+        <v>964155071</v>
       </c>
       <c r="X57" s="1" t="n">
         <v>0</v>
@@ -7860,16 +7860,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC57" s="1" t="n">
-        <v>0.960209634427359</v>
+        <v>0.599649</v>
       </c>
       <c r="AD57" s="1" t="n">
-        <v>0.960209634427359</v>
+        <v>0.599649</v>
       </c>
       <c r="AE57" s="1" t="n">
-        <v>0.960209634427359</v>
+        <v>0.599649</v>
       </c>
       <c r="AF57" s="1" t="n">
-        <v>0.960209634427359</v>
+        <v>0.599649</v>
       </c>
       <c r="AG57" s="1" t="n">
         <v>0.721490465456529</v>
@@ -7902,7 +7902,7 @@
         <v>0.503907097543282</v>
       </c>
       <c r="AW57" s="1" t="n">
-        <v>0.721490465456529</v>
+        <v>0.599649</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7970,7 +7970,7 @@
         <v>0.722542818686296</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>2750000000</v>
+        <v>1324579179</v>
       </c>
       <c r="X58" s="1" t="n">
         <v>0</v>
@@ -7988,16 +7988,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC58" s="1" t="n">
-        <v>0.973293450906066</v>
+        <v>0.673604</v>
       </c>
       <c r="AD58" s="1" t="n">
-        <v>0.973293450906066</v>
+        <v>0.673604</v>
       </c>
       <c r="AE58" s="1" t="n">
-        <v>0.973293450906066</v>
+        <v>0.673604</v>
       </c>
       <c r="AF58" s="1" t="n">
-        <v>0.973293450906066</v>
+        <v>0.673604</v>
       </c>
       <c r="AG58" s="1" t="n">
         <v>0.730870851594115</v>
@@ -8030,7 +8030,7 @@
         <v>0.5186715755013</v>
       </c>
       <c r="AW58" s="1" t="n">
-        <v>0.730870851594115</v>
+        <v>0.673604</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8098,7 +8098,7 @@
         <v>0.736122288420686</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>2750000000</v>
+        <v>1819738394</v>
       </c>
       <c r="X59" s="1" t="n">
         <v>0</v>
@@ -8116,16 +8116,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC59" s="1" t="n">
-        <v>0.986555547468112</v>
+        <v>0.756679</v>
       </c>
       <c r="AD59" s="1" t="n">
-        <v>0.986555547468112</v>
+        <v>0.756679</v>
       </c>
       <c r="AE59" s="1" t="n">
-        <v>0.986555547468112</v>
+        <v>0.756679</v>
       </c>
       <c r="AF59" s="1" t="n">
-        <v>0.986555547468112</v>
+        <v>0.756679</v>
       </c>
       <c r="AG59" s="1" t="n">
         <v>0.740373195884031</v>
@@ -8158,7 +8158,7 @@
         <v>0.533868652663489</v>
       </c>
       <c r="AW59" s="1" t="n">
-        <v>0.740373195884031</v>
+        <v>0.756679</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8226,7 +8226,7 @@
         <v>0.749956970709265</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>2750000000</v>
+        <v>2499999907</v>
       </c>
       <c r="X60" s="1" t="n">
         <v>0</v>
@@ -8244,16 +8244,16 @@
         <v>5500000000</v>
       </c>
       <c r="AC60" s="1" t="n">
-        <v>0.999998353357913</v>
+        <v>0.85</v>
       </c>
       <c r="AD60" s="1" t="n">
-        <v>0.999998353357913</v>
+        <v>0.85</v>
       </c>
       <c r="AE60" s="1" t="n">
-        <v>0.999998353357913</v>
+        <v>0.85</v>
       </c>
       <c r="AF60" s="1" t="n">
-        <v>0.999998353357913</v>
+        <v>0.85</v>
       </c>
       <c r="AG60" s="1" t="n">
         <v>0.75</v>
@@ -8292,7 +8292,7 @@
         <v>0.549511004186529</v>
       </c>
       <c r="AW60" s="1" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
